--- a/Estoque_Empresas_Ananindeua_Capanema.xlsx
+++ b/Estoque_Empresas_Ananindeua_Capanema.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +34,47 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A5E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2A5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +89,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +471,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -438,68 +481,68 @@
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ESTOQUE DE ESTABELECIMENTOS (CNPJ ATIVOS) — ANANINDEUA — 2000 A 2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Estabelecimentos com CNPJ ativo (situação 02) em Jul/2026, por data de abertura. Fonte: CNPJ Receita Federal. Equivalente adaptado ao RAIS ESTAB (não baixado nesta série).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2000</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2005</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2010</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2015</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2020</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2025</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Δ%
 2000→2025</t>
@@ -507,771 +550,776 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>1428.6%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>156</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>286</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>661</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="7" t="n">
         <v>1383</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="7" t="n">
         <v>3194</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>2629.9%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="7" t="n">
         <v>148</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>2366.7%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="9" t="n">
         <v>148</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="9" t="n">
         <v>246</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>490</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="9" t="n">
         <v>1081</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>2594</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>2468.3%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>420</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>674</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>1250</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2719</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>5947</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>12815</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>2951.2%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="9" t="n">
         <v>173</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>372</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="9" t="n">
         <v>955</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="9" t="n">
         <v>4350</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>7667.9%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>325</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>1032</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>3270</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>20337.5%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="9" t="n">
         <v>590</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>5800.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>1033.3%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="9" t="n">
         <v>104</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="9" t="n">
         <v>192</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>1180.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="7" t="n">
         <v>265</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="7" t="n">
         <v>784</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="7" t="n">
         <v>2328</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>8214.3%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="9" t="n">
         <v>108</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="9" t="n">
         <v>198</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="9" t="n">
         <v>430</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="9" t="n">
         <v>902</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="9" t="n">
         <v>2191</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>3122.1%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>487.5%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="9" t="n">
         <v>233</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="9" t="n">
         <v>482</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="9" t="n">
         <v>1408</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>2773.5%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="7" t="n">
         <v>165</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="7" t="n">
         <v>292</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>2544.8%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="9" t="n">
         <v>418</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>1572.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>295</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="7" t="n">
         <v>372</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="7" t="n">
         <v>505</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="7" t="n">
         <v>861</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
         <v>1683</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="7" t="n">
         <v>3520</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>1093.2%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="9" t="n">
         <v>155</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>1278</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="9" t="n">
         <v>1884</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="9" t="n">
         <v>3284</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="9" t="n">
         <v>6888</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="9" t="n">
         <v>15277</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="9" t="n">
         <v>38319</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>2898.4%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1286,7 +1334,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1296,68 +1344,68 @@
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ESTOQUE DE ESTABELECIMENTOS (CNPJ ATIVOS) — CAPANEMA — 2000 A 2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Estabelecimentos com CNPJ ativo (situação 02) em Jul/2026, por data de abertura. Fonte: CNPJ Receita Federal. Equivalente adaptado ao RAIS ESTAB (não baixado nesta série).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2000</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2005</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2010</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2015</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2020</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2025</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Δ%
 2000→2025</t>
@@ -1365,771 +1413,776 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>766.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="7" t="n">
         <v>169</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="7" t="n">
         <v>353</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>3822.2%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>300.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="9" t="n">
         <v>117</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>235</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>3816.7%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>249</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>1267</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>2446</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>3297.2%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="9" t="n">
         <v>142</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="9" t="n">
         <v>315</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>5150.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>179</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>368</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>36700.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>2850.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>440.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>900.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="7" t="n">
         <v>317</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>3070.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="9" t="n">
         <v>237</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>5825.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="9" t="n">
         <v>148</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>1750.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>3025.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>2000.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
         <v>334</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="7" t="n">
         <v>513</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>654.4%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>219</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="9" t="n">
         <v>334</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="9" t="n">
         <v>612</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="9" t="n">
         <v>1402</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="9" t="n">
         <v>2695</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="9" t="n">
         <v>5306</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>2322.8%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2144,7 +2197,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2154,68 +2207,68 @@
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ESTOQUE DE ESTABELECIMENTOS (CNPJ ATIVOS) — PARÁ — 2000 A 2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Estabelecimentos com CNPJ ativo (situação 02) em Jul/2026, por data de abertura. Fonte: CNPJ Receita Federal. Equivalente adaptado ao RAIS ESTAB (não baixado nesta série).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2000</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2005</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2010</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2015</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2020</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Estab.
 2025</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Δ%
 2000→2025</t>
@@ -2223,771 +2276,776 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>473</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>634</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>906</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>1323</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="7" t="n">
         <v>2084</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7" t="n">
         <v>5263</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>1012.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="9" t="n">
         <v>144</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="9" t="n">
         <v>235</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>344</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="9" t="n">
         <v>518</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>750.5%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>1264</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>1835</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>3228</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>7019</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="7" t="n">
         <v>14483</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="7" t="n">
         <v>32604</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>2479.4%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="9" t="n">
         <v>222</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="9" t="n">
         <v>274</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="9" t="n">
         <v>288</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>308</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="9" t="n">
         <v>361</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="9" t="n">
         <v>478</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>115.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>320</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="7" t="n">
         <v>565</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="7" t="n">
         <v>1270</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>1086.9%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>904</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="9" t="n">
         <v>1421</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="9" t="n">
         <v>2486</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>5381</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="9" t="n">
         <v>11241</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>26836</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>2868.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>6795</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>10932</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>19322</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>40328</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>82502</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>178329</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>2524.4%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="9" t="n">
         <v>786</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="9" t="n">
         <v>1191</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="9" t="n">
         <v>1931</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>3869</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="9" t="n">
         <v>8921</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="9" t="n">
         <v>30574</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>3789.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>502</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>779</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>1538</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>4474</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>12195</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>35276</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>6927.1%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="9" t="n">
         <v>262</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="9" t="n">
         <v>398</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="9" t="n">
         <v>686</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="9" t="n">
         <v>1327</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="9" t="n">
         <v>2955</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="9" t="n">
         <v>7580</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>2793.1%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>449</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>607</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>804</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>1227</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="7" t="n">
         <v>1745</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="7" t="n">
         <v>3257</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>625.4%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="9" t="n">
         <v>290</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="9" t="n">
         <v>490</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="9" t="n">
         <v>930</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="9" t="n">
         <v>1531</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="9" t="n">
         <v>2855</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>1279.2%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="7" t="n">
         <v>862</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="7" t="n">
         <v>1302</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="7" t="n">
         <v>2304</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="7" t="n">
         <v>4521</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="7" t="n">
         <v>10810</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="7" t="n">
         <v>28569</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>3214.3%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="9" t="n">
         <v>1513</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="9" t="n">
         <v>2094</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="9" t="n">
         <v>3108</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="9" t="n">
         <v>5520</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="9" t="n">
         <v>10682</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="9" t="n">
         <v>25379</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>1577.4%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="7" t="n">
         <v>974</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="7" t="n">
         <v>1274</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="7" t="n">
         <v>1510</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="7" t="n">
         <v>1758</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="7" t="n">
         <v>1946</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>143.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="9" t="n">
         <v>710</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="9" t="n">
         <v>1191</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="9" t="n">
         <v>2195</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="9" t="n">
         <v>3517</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="9" t="n">
         <v>6524</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="9" t="n">
         <v>15520</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>2085.9%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="7" t="n">
         <v>756</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="7" t="n">
         <v>1091</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="7" t="n">
         <v>1853</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="7" t="n">
         <v>3206</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="7" t="n">
         <v>5711</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="7" t="n">
         <v>12811</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>1594.6%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="9" t="n">
         <v>407</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="9" t="n">
         <v>538</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="9" t="n">
         <v>758</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="9" t="n">
         <v>1291</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="9" t="n">
         <v>2490</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="9" t="n">
         <v>5668</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>1292.6%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>6067</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="7" t="n">
         <v>9122</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="7" t="n">
         <v>12974</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="7" t="n">
         <v>19678</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
         <v>28926</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="7" t="n">
         <v>48784</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>704.1%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="9" t="n">
         <v>289</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="9" t="n">
         <v>1019</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>23189</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="9" t="n">
         <v>34958</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="9" t="n">
         <v>56576</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="9" t="n">
         <v>106127</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="9" t="n">
         <v>206297</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="9" t="n">
         <v>464866</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>1904.7%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Estoque_Empresas_Ananindeua_Capanema.xlsx
+++ b/Estoque_Empresas_Ananindeua_Capanema.xlsx
@@ -561,26 +561,26 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>1428.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -596,26 +596,26 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -631,26 +631,26 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>661</v>
+        <v>627</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1383</v>
+        <v>1339</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>3194</v>
+        <v>3128</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>2629.9%</t>
+          <t>3059.6%</t>
         </is>
       </c>
     </row>
@@ -666,26 +666,26 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -701,26 +701,26 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>2366.7%</t>
+          <t>2660.0%</t>
         </is>
       </c>
     </row>
@@ -736,26 +736,26 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1081</v>
+        <v>1026</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2594</v>
+        <v>2496</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2468.3%</t>
+          <t>2583.9%</t>
         </is>
       </c>
     </row>
@@ -771,26 +771,26 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>674</v>
+        <v>582</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1250</v>
+        <v>1105</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2719</v>
+        <v>2491</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>5947</v>
+        <v>5522</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>12815</v>
+        <v>12046</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>2951.2%</t>
+          <t>3182.3%</t>
         </is>
       </c>
     </row>
@@ -806,26 +806,26 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>372</v>
+        <v>309</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>955</v>
+        <v>868</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>4350</v>
+        <v>4209</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>7667.9%</t>
+          <t>10165.9%</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
         <v>16</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1032</v>
+        <v>1006</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>3270</v>
+        <v>3213</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>20337.5%</t>
+          <t>19981.2%</t>
         </is>
       </c>
     </row>
@@ -882,20 +882,20 @@
         <v>17</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>5800.0%</t>
+          <t>5640.0%</t>
         </is>
       </c>
     </row>
@@ -911,26 +911,26 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>26</v>
-      </c>
       <c r="E14" s="7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>1033.3%</t>
+          <t>1490.9%</t>
         </is>
       </c>
     </row>
@@ -946,26 +946,26 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1180.0%</t>
+          <t>1250.0%</t>
         </is>
       </c>
     </row>
@@ -981,26 +981,26 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>2328</v>
+        <v>2310</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>8214.3%</t>
+          <t>8455.6%</t>
         </is>
       </c>
     </row>
@@ -1016,26 +1016,26 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>902</v>
+        <v>866</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>2191</v>
+        <v>2120</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>3122.1%</t>
+          <t>3161.5%</t>
         </is>
       </c>
     </row>
@@ -1051,26 +1051,26 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>14</v>
-      </c>
       <c r="E18" s="7" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>487.5%</t>
+          <t>720.0%</t>
         </is>
       </c>
     </row>
@@ -1086,26 +1086,26 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>482</v>
+        <v>449</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1408</v>
+        <v>1356</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2773.5%</t>
+          <t>3290.0%</t>
         </is>
       </c>
     </row>
@@ -1121,26 +1121,26 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>292</v>
+        <v>237</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>767</v>
+        <v>683</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>2544.8%</t>
+          <t>3152.4%</t>
         </is>
       </c>
     </row>
@@ -1156,26 +1156,26 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1572.0%</t>
+          <t>1600.0%</t>
         </is>
       </c>
     </row>
@@ -1191,26 +1191,26 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>295</v>
+        <v>224</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>372</v>
+        <v>288</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>505</v>
+        <v>410</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>861</v>
+        <v>739</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1683</v>
+        <v>1539</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>3520</v>
+        <v>3344</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>1093.2%</t>
+          <t>1392.9%</t>
         </is>
       </c>
     </row>
@@ -1292,26 +1292,26 @@
       </c>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n">
-        <v>1278</v>
+        <v>1062</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1884</v>
+        <v>1575</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>3284</v>
+        <v>2843</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>6888</v>
+        <v>6258</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>15277</v>
+        <v>14275</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>38319</v>
+        <v>36590</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2898.4%</t>
+          <t>3345.4%</t>
         </is>
       </c>
     </row>
@@ -1424,26 +1424,26 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>766.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1459,26 +1459,26 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1494,26 +1494,26 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>3822.2%</t>
+          <t>4814.3%</t>
         </is>
       </c>
     </row>
@@ -1529,26 +1529,26 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1564,26 +1564,26 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="H8" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1599,26 +1599,26 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>3816.7%</t>
+          <t>5675.0%</t>
         </is>
       </c>
     </row>
@@ -1634,26 +1634,26 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>637</v>
+        <v>599</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>2446</v>
+        <v>2315</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3297.2%</t>
+          <t>3517.2%</t>
         </is>
       </c>
     </row>
@@ -1669,26 +1669,26 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>5150.0%</t>
+          <t>7150.0%</t>
         </is>
       </c>
     </row>
@@ -1716,14 +1716,14 @@
         <v>69</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>36700.0%</t>
+          <t>35900.0%</t>
         </is>
       </c>
     </row>
@@ -1745,20 +1745,20 @@
         <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2850.0%</t>
+          <t>2400.0%</t>
         </is>
       </c>
     </row>
@@ -1774,26 +1774,26 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>13</v>
-      </c>
       <c r="H14" s="7" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>440.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1824,11 +1824,11 @@
         <v>14</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>900.0%</t>
+          <t>850.0%</t>
         </is>
       </c>
     </row>
@@ -1853,17 +1853,17 @@
         <v>27</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3070.0%</t>
+          <t>3000.0%</t>
         </is>
       </c>
     </row>
@@ -1882,23 +1882,23 @@
         <v>4</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>5825.0%</t>
+          <t>5550.0%</t>
         </is>
       </c>
     </row>
@@ -1914,26 +1914,26 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>11</v>
-      </c>
       <c r="E18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>14</v>
-      </c>
       <c r="H18" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -1949,26 +1949,26 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1750.0%</t>
+          <t>2150.0%</t>
         </is>
       </c>
     </row>
@@ -1990,20 +1990,20 @@
         <v>9</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3025.0%</t>
+          <t>2600.0%</t>
         </is>
       </c>
     </row>
@@ -2028,17 +2028,17 @@
         <v>5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2000.0%</t>
+          <t>1933.3%</t>
         </is>
       </c>
     </row>
@@ -2054,26 +2054,26 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>654.4%</t>
+          <t>695.2%</t>
         </is>
       </c>
     </row>
@@ -2155,26 +2155,26 @@
       </c>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>612</v>
+        <v>546</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1402</v>
+        <v>1303</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>2695</v>
+        <v>2538</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>5306</v>
+        <v>5008</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2322.8%</t>
+          <t>2651.6%</t>
         </is>
       </c>
     </row>
@@ -2287,26 +2287,26 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>906</v>
+        <v>0</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1323</v>
+        <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2084</v>
+        <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>5263</v>
+        <v>0</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>1012.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2322,26 +2322,26 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>842</v>
+        <v>0</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>750.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2357,26 +2357,26 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1264</v>
+        <v>1062</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1835</v>
+        <v>1571</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3228</v>
+        <v>2875</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>7019</v>
+        <v>6544</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>14483</v>
+        <v>13846</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>32604</v>
+        <v>31574</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>2479.4%</t>
+          <t>2873.1%</t>
         </is>
       </c>
     </row>
@@ -2392,26 +2392,26 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>222</v>
+        <v>3</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>274</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>288</v>
+        <v>14</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>361</v>
+        <v>47</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>478</v>
+        <v>93</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>3000.0%</t>
         </is>
       </c>
     </row>
@@ -2427,26 +2427,26 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>320</v>
+        <v>226</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>565</v>
+        <v>460</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>1270</v>
+        <v>1119</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>1086.9%</t>
+          <t>3191.2%</t>
         </is>
       </c>
     </row>
@@ -2462,26 +2462,26 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>904</v>
+        <v>808</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1421</v>
+        <v>1295</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2486</v>
+        <v>2282</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>5381</v>
+        <v>4993</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>11241</v>
+        <v>10674</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>26836</v>
+        <v>25822</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2868.6%</t>
+          <t>3095.8%</t>
         </is>
       </c>
     </row>
@@ -2497,26 +2497,26 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>6795</v>
+        <v>6030</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>10932</v>
+        <v>9734</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>19322</v>
+        <v>17446</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>40328</v>
+        <v>37187</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>82502</v>
+        <v>77046</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>178329</v>
+        <v>167566</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>2524.4%</t>
+          <t>2678.9%</t>
         </is>
       </c>
     </row>
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>786</v>
+        <v>468</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1191</v>
+        <v>733</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1931</v>
+        <v>1321</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>3869</v>
+        <v>3014</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>8921</v>
+        <v>7698</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>30574</v>
+        <v>28433</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>3789.8%</t>
+          <t>5975.4%</t>
         </is>
       </c>
     </row>
@@ -2567,26 +2567,26 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>779</v>
+        <v>734</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1538</v>
+        <v>1449</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4474</v>
+        <v>4313</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12195</v>
+        <v>11866</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>35276</v>
+        <v>34422</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>6927.1%</t>
+          <t>7208.3%</t>
         </is>
       </c>
     </row>
@@ -2602,26 +2602,26 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>686</v>
+        <v>636</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1327</v>
+        <v>1207</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>2955</v>
+        <v>2673</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>7580</v>
+        <v>6985</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2793.1%</t>
+          <t>2751.0%</t>
         </is>
       </c>
     </row>
@@ -2637,26 +2637,26 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>449</v>
+        <v>196</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>607</v>
+        <v>296</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>804</v>
+        <v>407</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1227</v>
+        <v>625</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1745</v>
+        <v>1000</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3257</v>
+        <v>2264</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>625.4%</t>
+          <t>1055.1%</t>
         </is>
       </c>
     </row>
@@ -2672,26 +2672,26 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>1531</v>
+        <v>1501</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>2855</v>
+        <v>2778</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1279.2%</t>
+          <t>1268.5%</t>
         </is>
       </c>
     </row>
@@ -2707,26 +2707,26 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>862</v>
+        <v>811</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1302</v>
+        <v>1232</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2304</v>
+        <v>2202</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>4521</v>
+        <v>4326</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>10810</v>
+        <v>10506</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>28569</v>
+        <v>27891</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3214.3%</t>
+          <t>3339.1%</t>
         </is>
       </c>
     </row>
@@ -2742,26 +2742,26 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1513</v>
+        <v>1453</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2094</v>
+        <v>1989</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>3108</v>
+        <v>2883</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>5520</v>
+        <v>5157</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>10682</v>
+        <v>10088</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>25379</v>
+        <v>24208</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1577.4%</t>
+          <t>1566.1%</t>
         </is>
       </c>
     </row>
@@ -2777,26 +2777,26 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>800</v>
+        <v>681</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>974</v>
+        <v>814</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1274</v>
+        <v>1054</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>1510</v>
+        <v>1264</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1758</v>
+        <v>1494</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1946</v>
+        <v>1663</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>143.2%</t>
+          <t>144.2%</t>
         </is>
       </c>
     </row>
@@ -2812,26 +2812,26 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>710</v>
+        <v>628</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1191</v>
+        <v>1075</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2195</v>
+        <v>1982</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>3517</v>
+        <v>3157</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>6524</v>
+        <v>5955</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>15520</v>
+        <v>14583</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2085.9%</t>
+          <t>2222.1%</t>
         </is>
       </c>
     </row>
@@ -2847,26 +2847,26 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>756</v>
+        <v>624</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1091</v>
+        <v>926</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1853</v>
+        <v>1612</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>3206</v>
+        <v>2823</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>5711</v>
+        <v>5088</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>12811</v>
+        <v>11651</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>1594.6%</t>
+          <t>1767.1%</t>
         </is>
       </c>
     </row>
@@ -2882,26 +2882,26 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>538</v>
+        <v>513</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>758</v>
+        <v>725</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1291</v>
+        <v>1246</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>2490</v>
+        <v>2425</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>5668</v>
+        <v>5512</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1292.6%</t>
+          <t>1328.0%</t>
         </is>
       </c>
     </row>
@@ -2917,26 +2917,26 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>6067</v>
+        <v>5319</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>9122</v>
+        <v>8166</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>12974</v>
+        <v>11782</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>19678</v>
+        <v>18205</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>28926</v>
+        <v>27203</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>48784</v>
+        <v>46738</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>704.1%</t>
+          <t>778.7%</t>
         </is>
       </c>
     </row>
@@ -3018,26 +3018,26 @@
       </c>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n">
-        <v>23189</v>
+        <v>19426</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>34958</v>
+        <v>29807</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>56576</v>
+        <v>49263</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>106127</v>
+        <v>95255</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>206297</v>
+        <v>189865</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>464866</v>
+        <v>434327</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>1904.7%</t>
+          <t>2135.8%</t>
         </is>
       </c>
     </row>
